--- a/resources/logistics/templates/speeda-outbound-v1.xlsx
+++ b/resources/logistics/templates/speeda-outbound-v1.xlsx
@@ -108,7 +108,7 @@
     <t>发件人税号</t>
   </si>
   <si>
-    <t>C39681-007</t>
+    <t>P7C-DEMO-0001</t>
   </si>
   <si>
     <t>SD标准挂号-带电</t>
@@ -117,22 +117,22 @@
     <t>Canada</t>
   </si>
   <si>
-    <t>Emily Cross</t>
-  </si>
-  <si>
-    <t>BC</t>
-  </si>
-  <si>
-    <t>Kelowna</t>
-  </si>
-  <si>
-    <t>5205 Cobble Court</t>
-  </si>
-  <si>
-    <t>emilycross@live.com</t>
-  </si>
-  <si>
-    <t>V1W 4Y8</t>
+    <t>Fictional Recipient 01</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>San Francisco</t>
+  </si>
+  <si>
+    <t>123 Demo Street</t>
+  </si>
+  <si>
+    <t>recipient01@example.invalid</t>
+  </si>
+  <si>
+    <t>94105</t>
   </si>
   <si>
     <t>hand held massager</t>
@@ -141,277 +141,277 @@
     <t>手持按摩器</t>
   </si>
   <si>
-    <t>KOL26082203-007</t>
+    <t>P7C-REDACTED-UNUSED-0035</t>
   </si>
   <si>
     <t>Philippines</t>
   </si>
   <si>
-    <t>Cristian Partoza</t>
-  </si>
-  <si>
-    <t>Rizal</t>
-  </si>
-  <si>
-    <t>Cainta</t>
-  </si>
-  <si>
-    <t>046 Victoria Street San Juan</t>
-  </si>
-  <si>
-    <t>639675824336</t>
-  </si>
-  <si>
-    <t>kaheyyuga@gmail.com</t>
-  </si>
-  <si>
-    <t>KOL26082304-007</t>
-  </si>
-  <si>
-    <t>Norton mcnaughton</t>
-  </si>
-  <si>
-    <t>Ontario</t>
-  </si>
-  <si>
-    <t>richmondhill</t>
-  </si>
-  <si>
-    <t>12 kingshill road</t>
-  </si>
-  <si>
-    <t>emb4lmr@gmail.com</t>
-  </si>
-  <si>
-    <t>L4E 4b1</t>
-  </si>
-  <si>
-    <t>KOL26082306-007</t>
-  </si>
-  <si>
-    <t>Ash Ash</t>
-  </si>
-  <si>
-    <t>NCR</t>
-  </si>
-  <si>
-    <t>Taguig City</t>
-  </si>
-  <si>
-    <t>3G R. Magsaysay St AFPOVAI</t>
-  </si>
-  <si>
-    <t>09568954177</t>
-  </si>
-  <si>
-    <t>awkwartt@gmail.com</t>
-  </si>
-  <si>
-    <t>C39729-007</t>
-  </si>
-  <si>
-    <t>Brandon Cardwell</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>Edmonton</t>
-  </si>
-  <si>
-    <t>13532 111 Street Northwest</t>
-  </si>
-  <si>
-    <t>hatchethauling31@gmail.com</t>
-  </si>
-  <si>
-    <t>T5E 4Z8</t>
-  </si>
-  <si>
-    <t>C39733-007</t>
-  </si>
-  <si>
-    <t>SD经济挂号-带电</t>
-  </si>
-  <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>Shala Cameron</t>
-  </si>
-  <si>
-    <t>TX</t>
-  </si>
-  <si>
-    <t>Ben Wheeler</t>
-  </si>
-  <si>
-    <t>610 Vz County Rd 4714</t>
-  </si>
-  <si>
-    <t>kadanandskye@gmail.com</t>
-  </si>
-  <si>
-    <t>Silicone toy</t>
-  </si>
-  <si>
-    <t>硅胶玩具</t>
-  </si>
-  <si>
-    <t>C39734-007</t>
+    <t>P7C-REDACTED-UNUSED-0037</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0038</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0039</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0040</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0041</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0042</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0043</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0044</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0045</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0046</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0047</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0048</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0049</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0050</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0051</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0052</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0053</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0054</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0055</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0056</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0057</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0058</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0059</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0060</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0061</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0062</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0063</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0064</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0065</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0066</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0067</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0068</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0069</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0070</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0071</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0072</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0073</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0074</t>
   </si>
   <si>
     <t>Germany</t>
   </si>
   <si>
-    <t>Andrea Dürst</t>
-  </si>
-  <si>
-    <t>DE-SN</t>
-  </si>
-  <si>
-    <t>Dresden</t>
-  </si>
-  <si>
-    <t>Wiener Straße 96</t>
-  </si>
-  <si>
-    <t>4915172918904</t>
-  </si>
-  <si>
-    <t>pandy524durst@gmail.com</t>
-  </si>
-  <si>
-    <t>01219</t>
-  </si>
-  <si>
-    <t>IOSS</t>
-  </si>
-  <si>
-    <t>IM4420001405</t>
-  </si>
-  <si>
-    <t>C39740-007</t>
-  </si>
-  <si>
-    <t>Belgium</t>
-  </si>
-  <si>
-    <t>Aäron Belderbos</t>
-  </si>
-  <si>
-    <t>Sint-Gillis-Waas</t>
-  </si>
-  <si>
-    <t>Kerselarendreef 64</t>
-  </si>
-  <si>
-    <t>belderbos.aaron@gmail.com</t>
-  </si>
-  <si>
-    <t>C39744-007</t>
+    <t>P7C-REDACTED-UNUSED-0076</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0077</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0078</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0079</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0080</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0081</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0082</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0083</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0084</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0085</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0086</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0087</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0088</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0089</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0090</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0091</t>
   </si>
   <si>
     <t>Australia</t>
   </si>
   <si>
-    <t>Vanessa Shields</t>
-  </si>
-  <si>
-    <t>NSW</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>8 Brighton Avenue Unit 5</t>
-  </si>
-  <si>
-    <t>0421702787</t>
-  </si>
-  <si>
-    <t>plotter_cycle1b@icloud.com</t>
-  </si>
-  <si>
-    <t>C39745-007</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Lenny Chukukere</t>
-  </si>
-  <si>
-    <t>Erith</t>
-  </si>
-  <si>
-    <t>18 silver spring close</t>
-  </si>
-  <si>
-    <t>447482307565</t>
-  </si>
-  <si>
-    <t>lchukukere@gmail.com</t>
-  </si>
-  <si>
-    <t>DA8 1EQ</t>
-  </si>
-  <si>
-    <t>C39757-007</t>
-  </si>
-  <si>
-    <t>Alltagsheld Marina Pandzic</t>
-  </si>
-  <si>
-    <t>DE-HE</t>
-  </si>
-  <si>
-    <t>Viernheim</t>
-  </si>
-  <si>
-    <t>Kirschenstraße 48a</t>
-  </si>
-  <si>
-    <t>4917624749302</t>
-  </si>
-  <si>
-    <t>marina_pandzic@gmx.de</t>
-  </si>
-  <si>
-    <t>C39758-007</t>
-  </si>
-  <si>
-    <t>Finn Egolf</t>
-  </si>
-  <si>
-    <t>Weingarten</t>
-  </si>
-  <si>
-    <t>Pfarrer-Nikolaus-Straße 42</t>
-  </si>
-  <si>
-    <t>4915758245644</t>
-  </si>
-  <si>
-    <t>finn.egolf@proton.me</t>
-  </si>
-  <si>
-    <t>C39769-007</t>
-  </si>
-  <si>
-    <t>Riley Oberbroeckling</t>
+    <t>P7C-REDACTED-UNUSED-0093</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0094</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0095</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0096</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0097</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0098</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0099</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0100</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0101</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0102</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0103</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0104</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0105</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0106</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0107</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0108</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0109</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0110</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0111</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0112</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0113</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0114</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0115</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0116</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0117</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0118</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0119</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0120</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0121</t>
   </si>
   <si>
     <t>IL</t>
   </si>
   <si>
-    <t>Glenview</t>
-  </si>
-  <si>
-    <t>2219 Glenview Road</t>
-  </si>
-  <si>
-    <t>rileyoberbroeckling@gmail.com</t>
+    <t>P7C-REDACTED-UNUSED-0123</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0124</t>
+  </si>
+  <si>
+    <t>P7C-REDACTED-UNUSED-0125</t>
   </si>
   <si>
     <t>二字码</t>
@@ -4108,7 +4108,7 @@
         <v>30</v>
       </c>
       <c r="I2" s="12">
-        <v>2503141834</v>
+        <v>2025550101</v>
       </c>
       <c r="J2" s="15" t="s">
         <v>31</v>
